--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,285 +396,285 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>472</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>201</v>
+        <v>140</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>248</v>
+        <v>143</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>345</v>
+        <v>144</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>362</v>
+        <v>159</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>154</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>413</v>
+        <v>247</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>92</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>424</v>
+        <v>248</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>615</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>515</v>
+        <v>436</v>
       </c>
       <c r="B12">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>223</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>589</v>
+        <v>964</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>624</v>
+        <v>1050</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>976</v>
+        <v>1407</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>1309</v>
+        <v>1668</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1414</v>
+        <v>1801</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>112</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>1446</v>
+        <v>2328</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>142</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1490</v>
+        <v>2331</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1668</v>
+        <v>2423</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C20">
-        <v>111</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1728</v>
+        <v>2424</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C21">
-        <v>111</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2054</v>
+        <v>2912</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>518</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2055</v>
+        <v>3477</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>518</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>2805</v>
+        <v>3894</v>
       </c>
       <c r="B24">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>202</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>3257</v>
+        <v>3898</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>3430</v>
+        <v>3899</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>3477</v>
+        <v>4223</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -682,293 +682,293 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>3495</v>
+        <v>4232</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C28">
-        <v>1117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>3674</v>
+        <v>5165</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>269</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>3889</v>
+        <v>5452</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>125</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>3893</v>
+        <v>6158</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>3894</v>
+        <v>6359</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>645</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>3906</v>
+        <v>6575</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>196</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>4222</v>
+        <v>7558</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>5111</v>
+        <v>7887</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>49</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>5152</v>
+        <v>8216</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>5453</v>
+        <v>8283</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>114</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>5494</v>
+        <v>8650</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38">
-        <v>111</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>5577</v>
+        <v>8675</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>5733</v>
+        <v>8676</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40">
-        <v>56</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>6097</v>
+        <v>8915</v>
       </c>
       <c r="B41">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>6496</v>
+        <v>9085</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C42">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>6497</v>
+        <v>9358</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>7885</v>
+        <v>9507</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>155</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>7887</v>
+        <v>10993</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>153</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>8216</v>
+        <v>11427</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>97</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>8356</v>
+        <v>11684</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>8753</v>
+        <v>11738</v>
       </c>
       <c r="B48">
         <v>2</v>
       </c>
       <c r="C48">
-        <v>392</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>8754</v>
+        <v>11739</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49">
-        <v>395</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>8926</v>
+        <v>11773</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>8944</v>
+        <v>11952</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>245</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>8963</v>
+        <v>12343</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52">
-        <v>97</v>
+        <v>995</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>9253</v>
+        <v>12351</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>506</v>
+        <v>700</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>10148</v>
+        <v>12511</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -979,73 +979,73 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>11690</v>
+        <v>12720</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>353</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>11767</v>
+        <v>12764</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>11848</v>
+        <v>12924</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>164</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>11868</v>
+        <v>12925</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>11952</v>
+        <v>13244</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>218</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>12222</v>
+        <v>18964</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>12511</v>
+        <v>20650</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -1056,156 +1056,35 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>12574</v>
+        <v>22364</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>224</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>12612</v>
+        <v>23992</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C63">
-        <v>72</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>12720</v>
+        <v>24566</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65">
-        <v>12764</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66">
-        <v>13028</v>
-      </c>
-      <c r="B66">
-        <v>3</v>
-      </c>
-      <c r="C66">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>13293</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
-      </c>
-      <c r="C67">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>19980</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
-        <v>19981</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>20650</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="C70">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
-        <v>20978</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
-        <v>23235</v>
-      </c>
-      <c r="B72">
-        <v>29</v>
-      </c>
-      <c r="C72">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
-        <v>24566</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74">
-        <v>24567</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75">
-        <v>24889</v>
-      </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -407,24 +407,24 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -435,29 +435,29 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -468,56 +468,56 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>340</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>720</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12">
-        <v>150</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -528,7 +528,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -539,40 +539,40 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>221</v>
+        <v>305</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>25</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>305</v>
+        <v>414</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>307</v>
+        <v>434</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -583,128 +583,128 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>361</v>
+        <v>515</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>362</v>
+        <v>565</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>378</v>
+        <v>738</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>87</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>414</v>
+        <v>790</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>434</v>
+        <v>791</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>93</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>515</v>
+        <v>823</v>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>565</v>
+        <v>947</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>615</v>
+        <v>964</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>616</v>
+        <v>976</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>94</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>624</v>
+        <v>991</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>738</v>
+        <v>1007</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>19</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>791</v>
+        <v>1055</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -715,145 +715,145 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>823</v>
+        <v>1060</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>947</v>
+        <v>1134</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>964</v>
+        <v>1243</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>70</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1055</v>
+        <v>1414</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1060</v>
+        <v>1446</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1134</v>
+        <v>1490</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1413</v>
+        <v>1492</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1414</v>
+        <v>1504</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>49</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1446</v>
+        <v>1654</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1490</v>
+        <v>1656</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1492</v>
+        <v>1668</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1668</v>
+        <v>1801</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1801</v>
+        <v>2049</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>47</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -869,35 +869,35 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2328</v>
+        <v>2322</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2422</v>
+        <v>2331</v>
       </c>
       <c r="B47">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>18</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -908,26 +908,26 @@
         <v>29</v>
       </c>
       <c r="C48">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2424</v>
+        <v>2438</v>
       </c>
       <c r="B49">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2438</v>
+        <v>2859</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C50">
         <v>34</v>
@@ -935,736 +935,736 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2774</v>
+        <v>3016</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C51">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2776</v>
+        <v>3258</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C52">
-        <v>64</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2778</v>
+        <v>3434</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2859</v>
+        <v>3477</v>
       </c>
       <c r="B54">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2879</v>
+        <v>3478</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2912</v>
+        <v>3495</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>23</v>
+        <v>499</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2916</v>
+        <v>3893</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>15</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3016</v>
+        <v>3894</v>
       </c>
       <c r="B58">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>25</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3434</v>
+        <v>3898</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>86</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3478</v>
+        <v>3899</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3495</v>
+        <v>3905</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C61">
-        <v>495</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3670</v>
+        <v>4223</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3893</v>
+        <v>5080</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3894</v>
+        <v>5111</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>72</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3898</v>
+        <v>5152</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>3899</v>
+        <v>5490</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3905</v>
+        <v>5540</v>
       </c>
       <c r="B67">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5080</v>
+        <v>5577</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5111</v>
+        <v>5646</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5152</v>
+        <v>5649</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5490</v>
+        <v>5652</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5491</v>
+        <v>5654</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5540</v>
+        <v>5656</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>81</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5577</v>
+        <v>5736</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5585</v>
+        <v>6097</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C75">
-        <v>115</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5649</v>
+        <v>6158</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5652</v>
+        <v>6496</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5654</v>
+        <v>6497</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5656</v>
+        <v>6575</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>26</v>
+        <v>135</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5733</v>
+        <v>6629</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5736</v>
+        <v>7004</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6097</v>
+        <v>7007</v>
       </c>
       <c r="B82">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6098</v>
+        <v>7885</v>
       </c>
       <c r="B83">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6158</v>
+        <v>7886</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C84">
-        <v>165</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6494</v>
+        <v>8216</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6496</v>
+        <v>8650</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>19</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6575</v>
+        <v>8660</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>133</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>6936</v>
+        <v>8753</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>131</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>7004</v>
+        <v>8754</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>37</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7005</v>
+        <v>8915</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>39</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7706</v>
+        <v>8926</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>7886</v>
+        <v>8939</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8216</v>
+        <v>8963</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8649</v>
+        <v>9070</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>116</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8660</v>
+        <v>9087</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8672</v>
+        <v>9373</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C96">
-        <v>139</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8675</v>
+        <v>9459</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8753</v>
+        <v>9530</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C98">
-        <v>169</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>8853</v>
+        <v>10170</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>8926</v>
+        <v>10532</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C100">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>8939</v>
+        <v>10716</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>76</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9085</v>
+        <v>10993</v>
       </c>
       <c r="B102">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>9459</v>
+        <v>11134</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C103">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>9530</v>
+        <v>11402</v>
       </c>
       <c r="B104">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10716</v>
+        <v>11427</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>48</v>
+        <v>237</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11134</v>
+        <v>11492</v>
       </c>
       <c r="B106">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11234</v>
+        <v>11583</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C107">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11402</v>
+        <v>11619</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11427</v>
+        <v>11681</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11583</v>
+        <v>11738</v>
       </c>
       <c r="B110">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11619</v>
+        <v>11767</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11681</v>
+        <v>11773</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11773</v>
+        <v>11836</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>277</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11836</v>
+        <v>11846</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>346</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11952</v>
+        <v>11868</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>97</v>
+        <v>260</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12050</v>
+        <v>11952</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12294</v>
+        <v>12050</v>
       </c>
       <c r="B117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -1672,194 +1672,194 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12506</v>
+        <v>12222</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12511</v>
+        <v>12229</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12574</v>
+        <v>12503</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12923</v>
+        <v>12506</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12924</v>
+        <v>12511</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12925</v>
+        <v>12574</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>30</v>
+        <v>96</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12979</v>
+        <v>12612</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>13115</v>
+        <v>12764</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>349</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>13928</v>
+        <v>12923</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>18964</v>
+        <v>12924</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>19685</v>
+        <v>12925</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>19687</v>
+        <v>12979</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>19969</v>
+        <v>13115</v>
       </c>
       <c r="B130">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>19985</v>
+        <v>13293</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>61</v>
+        <v>267</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>20650</v>
+        <v>19685</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>20927</v>
+        <v>19969</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C133">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>21806</v>
+        <v>19985</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>21809</v>
+        <v>20650</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -1870,54 +1870,54 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>22361</v>
+        <v>20927</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>22364</v>
+        <v>21793</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>230</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>23235</v>
+        <v>21806</v>
       </c>
       <c r="B138">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>23380</v>
+        <v>21809</v>
       </c>
       <c r="B139">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>23645</v>
+        <v>22364</v>
       </c>
       <c r="B140">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -1925,46 +1925,68 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>23992</v>
+        <v>23235</v>
       </c>
       <c r="B141">
         <v>29</v>
       </c>
       <c r="C141">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>24257</v>
+        <v>23380</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C142">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>24566</v>
+        <v>23645</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C143">
-        <v>287</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>24670</v>
+        <v>23992</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>20</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145">
+        <v>24257</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="C145">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146">
+        <v>24566</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,106 +396,106 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>272</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>113</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>344</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -506,164 +506,164 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>336</v>
+        <v>221</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>345</v>
+        <v>307</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>385</v>
+        <v>345</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>413</v>
+        <v>378</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>40</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>515</v>
+        <v>417</v>
       </c>
       <c r="B16">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>565</v>
+        <v>424</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>68</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>589</v>
+        <v>435</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>126</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>738</v>
+        <v>436</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>790</v>
+        <v>515</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>791</v>
+        <v>565</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>823</v>
+        <v>589</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>947</v>
+        <v>616</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>20</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>951</v>
+        <v>624</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>952</v>
+        <v>738</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>976</v>
+        <v>790</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -671,65 +671,65 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>990</v>
+        <v>791</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>991</v>
+        <v>823</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1055</v>
+        <v>944</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1060</v>
+        <v>951</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30">
-        <v>21</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1243</v>
+        <v>976</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1309</v>
+        <v>991</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>26</v>
@@ -737,1077 +737,1077 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1407</v>
+        <v>1007</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33">
-        <v>15</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1458</v>
+        <v>1049</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1490</v>
+        <v>1050</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1504</v>
+        <v>1055</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>158</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1560</v>
+        <v>1060</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1576</v>
+        <v>1134</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1654</v>
+        <v>1409</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C39">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1656</v>
+        <v>1414</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C40">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1668</v>
+        <v>1446</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1801</v>
+        <v>1490</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2054</v>
+        <v>1654</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>222</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2203</v>
+        <v>1656</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2322</v>
+        <v>2109</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2328</v>
+        <v>2203</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>62</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2436</v>
+        <v>2331</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2438</v>
+        <v>2422</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C49">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2492</v>
+        <v>2423</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C50">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3016</v>
+        <v>2424</v>
       </c>
       <c r="B51">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3257</v>
+        <v>2438</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3434</v>
+        <v>2774</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>86</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3477</v>
+        <v>2778</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>25</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3495</v>
+        <v>2859</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C55">
-        <v>500</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3893</v>
+        <v>2879</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3894</v>
+        <v>3016</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C57">
-        <v>109</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3905</v>
+        <v>3257</v>
       </c>
       <c r="B58">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3906</v>
+        <v>3258</v>
       </c>
       <c r="B59">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C59">
-        <v>89</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4222</v>
+        <v>3430</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4223</v>
+        <v>3434</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5020</v>
+        <v>3477</v>
       </c>
       <c r="B62">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>237</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5111</v>
+        <v>3478</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5152</v>
+        <v>3495</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>12</v>
+        <v>486</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5490</v>
+        <v>3674</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>49</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5538</v>
+        <v>3893</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5577</v>
+        <v>3894</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5646</v>
+        <v>3898</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5647</v>
+        <v>3899</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5649</v>
+        <v>3905</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C70">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5654</v>
+        <v>4223</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6098</v>
+        <v>5020</v>
       </c>
       <c r="B72">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="C72">
-        <v>35</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6496</v>
+        <v>5152</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6497</v>
+        <v>5540</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6630</v>
+        <v>5577</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7004</v>
+        <v>5585</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>37</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7084</v>
+        <v>5646</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>79</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8155</v>
+        <v>5649</v>
       </c>
       <c r="B78">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8650</v>
+        <v>5652</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>173</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8659</v>
+        <v>5654</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8660</v>
+        <v>5733</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8754</v>
+        <v>5736</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>173</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8926</v>
+        <v>6098</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C83">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8963</v>
+        <v>6158</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9081</v>
+        <v>6497</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>231</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9087</v>
+        <v>6627</v>
       </c>
       <c r="B86">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9357</v>
+        <v>6630</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9373</v>
+        <v>6936</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>46</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9374</v>
+        <v>7005</v>
       </c>
       <c r="B89">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9459</v>
+        <v>7084</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>24</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9530</v>
+        <v>7704</v>
       </c>
       <c r="B91">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9778</v>
+        <v>7706</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10170</v>
+        <v>7885</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C93">
-        <v>26</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10532</v>
+        <v>8649</v>
       </c>
       <c r="B94">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>13</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10574</v>
+        <v>8660</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10716</v>
+        <v>8753</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>50</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10906</v>
+        <v>8754</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C97">
-        <v>8</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10994</v>
+        <v>8926</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11134</v>
+        <v>9085</v>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C99">
-        <v>8</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11427</v>
+        <v>9087</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>239</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11450</v>
+        <v>9373</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C101">
-        <v>231</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11492</v>
+        <v>9459</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11493</v>
+        <v>9530</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C103">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11619</v>
+        <v>10147</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11773</v>
+        <v>10170</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11813</v>
+        <v>10532</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11814</v>
+        <v>10716</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11836</v>
+        <v>10993</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>277</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11846</v>
+        <v>11134</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C109">
-        <v>132</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>12048</v>
+        <v>11234</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>8</v>
+        <v>88</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>12050</v>
+        <v>11402</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>12222</v>
+        <v>11427</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>10</v>
+        <v>241</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12253</v>
+        <v>11492</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12489</v>
+        <v>11619</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12503</v>
+        <v>11681</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>100</v>
+        <v>254</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12506</v>
+        <v>11767</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12511</v>
+        <v>11773</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12574</v>
+        <v>11836</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>97</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12609</v>
+        <v>11846</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>270</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12612</v>
+        <v>11868</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>272</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12764</v>
+        <v>12050</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>353</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12923</v>
+        <v>12222</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12924</v>
+        <v>12506</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12925</v>
+        <v>12511</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12952</v>
+        <v>12574</v>
       </c>
       <c r="B125">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12979</v>
+        <v>12612</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13028</v>
+        <v>12923</v>
       </c>
       <c r="B127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13030</v>
+        <v>12924</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>141</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13115</v>
+        <v>12925</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13269</v>
+        <v>13115</v>
       </c>
       <c r="B130">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -1815,68 +1815,68 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13271</v>
+        <v>13293</v>
       </c>
       <c r="B131">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>184</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>19685</v>
+        <v>18964</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>19969</v>
+        <v>19685</v>
       </c>
       <c r="B133">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>19981</v>
+        <v>19687</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>19985</v>
+        <v>19969</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C135">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19989</v>
+        <v>19985</v>
       </c>
       <c r="B136">
         <v>2</v>
       </c>
       <c r="C136">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -1903,54 +1903,54 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21752</v>
+        <v>21806</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21783</v>
+        <v>21809</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21793</v>
+        <v>22364</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21806</v>
+        <v>23380</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C142">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21809</v>
+        <v>23645</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -1958,112 +1958,46 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22364</v>
+        <v>23992</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22631</v>
+        <v>24257</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22634</v>
+        <v>24566</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>8</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23235</v>
+        <v>24670</v>
       </c>
       <c r="B147">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148">
-        <v>23380</v>
-      </c>
-      <c r="B148">
-        <v>29</v>
-      </c>
-      <c r="C148">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149">
-        <v>23539</v>
-      </c>
-      <c r="B149">
-        <v>3</v>
-      </c>
-      <c r="C149">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>23645</v>
-      </c>
-      <c r="B150">
-        <v>68</v>
-      </c>
-      <c r="C150">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>24566</v>
-      </c>
-      <c r="B151">
-        <v>1</v>
-      </c>
-      <c r="C151">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>24567</v>
-      </c>
-      <c r="B152">
-        <v>1</v>
-      </c>
-      <c r="C152">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>24725</v>
-      </c>
-      <c r="B153">
-        <v>2</v>
-      </c>
-      <c r="C153">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +402,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -424,7 +424,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -435,7 +435,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -451,739 +451,739 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>344</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>729</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>217</v>
+        <v>307</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>221</v>
+        <v>378</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>307</v>
+        <v>417</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>71</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>345</v>
+        <v>515</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>378</v>
+        <v>616</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>115</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>417</v>
+        <v>624</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>424</v>
+        <v>738</v>
       </c>
       <c r="B17">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>265</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>435</v>
+        <v>790</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>436</v>
+        <v>791</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>515</v>
+        <v>823</v>
       </c>
       <c r="B20">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>128</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>565</v>
+        <v>950</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>68</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>589</v>
+        <v>951</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>126</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>616</v>
+        <v>964</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C23">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>624</v>
+        <v>976</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>738</v>
+        <v>990</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>790</v>
+        <v>991</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>791</v>
+        <v>1049</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>823</v>
+        <v>1050</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>944</v>
+        <v>1055</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>951</v>
+        <v>1060</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>51</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>976</v>
+        <v>1134</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>991</v>
+        <v>1409</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C32">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1007</v>
+        <v>1413</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C33">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1049</v>
+        <v>1414</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>97</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1050</v>
+        <v>1446</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1055</v>
+        <v>1490</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1060</v>
+        <v>1654</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1134</v>
+        <v>1656</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1409</v>
+        <v>2049</v>
       </c>
       <c r="B39">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>29</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1414</v>
+        <v>2054</v>
       </c>
       <c r="B40">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>50</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1446</v>
+        <v>2057</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1490</v>
+        <v>2109</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1654</v>
+        <v>2203</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1656</v>
+        <v>2322</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2109</v>
+        <v>2328</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2203</v>
+        <v>2331</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2328</v>
+        <v>2422</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C47">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2331</v>
+        <v>2423</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C48">
-        <v>57</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="B49">
         <v>29</v>
       </c>
       <c r="C49">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2423</v>
+        <v>2438</v>
       </c>
       <c r="B50">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2424</v>
+        <v>2774</v>
       </c>
       <c r="B51">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>16</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2438</v>
+        <v>2778</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2774</v>
+        <v>2859</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C53">
-        <v>152</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2778</v>
+        <v>3016</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C54">
-        <v>126</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2859</v>
+        <v>3257</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2879</v>
+        <v>3258</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C56">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3016</v>
+        <v>3430</v>
       </c>
       <c r="B57">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C57">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3257</v>
+        <v>3434</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3258</v>
+        <v>3478</v>
       </c>
       <c r="B59">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3430</v>
+        <v>3576</v>
       </c>
       <c r="B60">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C60">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3434</v>
+        <v>3577</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C61">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3477</v>
+        <v>3674</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3478</v>
+        <v>3893</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3495</v>
+        <v>3894</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>486</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3674</v>
+        <v>3898</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>148</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>3893</v>
+        <v>3899</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3894</v>
+        <v>3905</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C67">
-        <v>109</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>3898</v>
+        <v>3906</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>3899</v>
+        <v>4222</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C69">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>3905</v>
+        <v>4223</v>
       </c>
       <c r="B70">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C70">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4223</v>
+        <v>5020</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5020</v>
+        <v>5152</v>
       </c>
       <c r="B72">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>238</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5152</v>
+        <v>5452</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1194,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="C74">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1216,7 +1216,7 @@
         <v>3</v>
       </c>
       <c r="C76">
-        <v>116</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1276,79 +1276,79 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5736</v>
+        <v>6098</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C82">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6098</v>
+        <v>6497</v>
       </c>
       <c r="B83">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6158</v>
+        <v>6575</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6497</v>
+        <v>6629</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6627</v>
+        <v>6630</v>
       </c>
       <c r="B86">
         <v>3</v>
       </c>
       <c r="C86">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6630</v>
+        <v>6936</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>50</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>6936</v>
+        <v>7004</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>171</v>
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1364,68 +1364,68 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7084</v>
+        <v>7007</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7704</v>
+        <v>7885</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C91">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>7706</v>
+        <v>8649</v>
       </c>
       <c r="B92">
         <v>2</v>
       </c>
       <c r="C92">
-        <v>83</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>7885</v>
+        <v>8660</v>
       </c>
       <c r="B93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8649</v>
+        <v>8673</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94">
-        <v>172</v>
+        <v>133</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8660</v>
+        <v>8675</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1447,7 +1447,7 @@
         <v>2</v>
       </c>
       <c r="C97">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1518,216 +1518,216 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10147</v>
+        <v>9760</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C104">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10170</v>
+        <v>9777</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10532</v>
+        <v>9778</v>
       </c>
       <c r="B106">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10716</v>
+        <v>10147</v>
       </c>
       <c r="B107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>10993</v>
+        <v>10170</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11134</v>
+        <v>10532</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C109">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11234</v>
+        <v>10716</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C110">
-        <v>88</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11402</v>
+        <v>11134</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C111">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11427</v>
+        <v>11234</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>241</v>
+        <v>87</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11492</v>
+        <v>11402</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11619</v>
+        <v>11427</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>77</v>
+        <v>243</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11681</v>
+        <v>11492</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>254</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11767</v>
+        <v>11619</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11773</v>
+        <v>11681</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>60</v>
+        <v>254</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11836</v>
+        <v>11683</v>
       </c>
       <c r="B118">
         <v>2</v>
       </c>
       <c r="C118">
-        <v>277</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11846</v>
+        <v>11773</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>270</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11868</v>
+        <v>11814</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>272</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12050</v>
+        <v>11868</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>182</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12222</v>
+        <v>12048</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12506</v>
+        <v>12050</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -1738,29 +1738,29 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12511</v>
+        <v>12222</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12574</v>
+        <v>12506</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12612</v>
+        <v>12511</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -1771,161 +1771,161 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12923</v>
+        <v>12574</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>18</v>
+        <v>98</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12924</v>
+        <v>12612</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12925</v>
+        <v>12764</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129">
-        <v>31</v>
+        <v>353</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13115</v>
+        <v>12923</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13293</v>
+        <v>12924</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>184</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>18964</v>
+        <v>12925</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>19685</v>
+        <v>12979</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>19687</v>
+        <v>13115</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>19969</v>
+        <v>13293</v>
       </c>
       <c r="B135">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>140</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19985</v>
+        <v>19685</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>61</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20650</v>
+        <v>19687</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20927</v>
+        <v>19969</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C138">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21806</v>
+        <v>19981</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21809</v>
+        <v>19985</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22364</v>
+        <v>20650</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -1936,68 +1936,112 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>23380</v>
+        <v>20927</v>
       </c>
       <c r="B142">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23645</v>
+        <v>21806</v>
       </c>
       <c r="B143">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23992</v>
+        <v>21809</v>
       </c>
       <c r="B144">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>24257</v>
+        <v>22364</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24566</v>
+        <v>23645</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C146">
-        <v>151</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
+        <v>23992</v>
+      </c>
+      <c r="B147">
+        <v>29</v>
+      </c>
+      <c r="C147">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>24566</v>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
         <v>24670</v>
       </c>
-      <c r="B147">
-        <v>1</v>
-      </c>
-      <c r="C147">
-        <v>34</v>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>24705</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>25960</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,95 +396,95 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>266</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>860</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -495,98 +495,98 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>307</v>
+        <v>221</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>378</v>
+        <v>248</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>115</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>417</v>
+        <v>307</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>216</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>515</v>
+        <v>308</v>
       </c>
       <c r="B14">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>131</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>616</v>
+        <v>345</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>48</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>624</v>
+        <v>361</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>738</v>
+        <v>378</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>790</v>
+        <v>413</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>791</v>
+        <v>414</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -594,54 +594,54 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>823</v>
+        <v>435</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>950</v>
+        <v>565</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>27</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>951</v>
+        <v>589</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>964</v>
+        <v>590</v>
       </c>
       <c r="B23">
         <v>15</v>
       </c>
       <c r="C23">
-        <v>104</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>976</v>
+        <v>790</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -649,945 +649,945 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>990</v>
+        <v>791</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>991</v>
+        <v>823</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1049</v>
+        <v>944</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1050</v>
+        <v>947</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1055</v>
+        <v>950</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1060</v>
+        <v>951</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1134</v>
+        <v>952</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1409</v>
+        <v>964</v>
       </c>
       <c r="B32">
         <v>15</v>
       </c>
       <c r="C32">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1413</v>
+        <v>976</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>92</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1414</v>
+        <v>1049</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1446</v>
+        <v>1050</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1490</v>
+        <v>1055</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1654</v>
+        <v>1060</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1656</v>
+        <v>1243</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2049</v>
+        <v>1409</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C39">
-        <v>252</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2054</v>
+        <v>1414</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C40">
-        <v>284</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2057</v>
+        <v>1429</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2109</v>
+        <v>1446</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2203</v>
+        <v>1490</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2322</v>
+        <v>1492</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2328</v>
+        <v>1668</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2331</v>
+        <v>1801</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2422</v>
+        <v>2050</v>
       </c>
       <c r="B47">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>65</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2423</v>
+        <v>2054</v>
       </c>
       <c r="B48">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2424</v>
+        <v>2188</v>
       </c>
       <c r="B49">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2438</v>
+        <v>2203</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2774</v>
+        <v>2331</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>154</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2778</v>
+        <v>2422</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2859</v>
+        <v>2423</v>
       </c>
       <c r="B53">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C53">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3016</v>
+        <v>2424</v>
       </c>
       <c r="B54">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C54">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3257</v>
+        <v>2438</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3258</v>
+        <v>2774</v>
       </c>
       <c r="B56">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3430</v>
+        <v>2879</v>
       </c>
       <c r="B57">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3434</v>
+        <v>2916</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3478</v>
+        <v>3016</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C59">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3576</v>
+        <v>3258</v>
       </c>
       <c r="B60">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C60">
-        <v>16</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3577</v>
+        <v>3430</v>
       </c>
       <c r="B61">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C61">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3674</v>
+        <v>3434</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>112</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3893</v>
+        <v>3477</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3894</v>
+        <v>3576</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C64">
-        <v>109</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3898</v>
+        <v>3674</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>3899</v>
+        <v>3894</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3905</v>
+        <v>3898</v>
       </c>
       <c r="B67">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>3906</v>
+        <v>3899</v>
       </c>
       <c r="B68">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>91</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>4222</v>
+        <v>3905</v>
       </c>
       <c r="B69">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>4223</v>
+        <v>4019</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5020</v>
+        <v>4232</v>
       </c>
       <c r="B71">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>234</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5152</v>
+        <v>5020</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C72">
-        <v>12</v>
+        <v>261</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5452</v>
+        <v>5111</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5540</v>
+        <v>5152</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5577</v>
+        <v>5490</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5585</v>
+        <v>5491</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5646</v>
+        <v>5493</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>26</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5649</v>
+        <v>5540</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>31</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5652</v>
+        <v>5577</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5654</v>
+        <v>5585</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5733</v>
+        <v>5652</v>
       </c>
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6098</v>
+        <v>5656</v>
       </c>
       <c r="B82">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>6497</v>
+        <v>5733</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6575</v>
+        <v>6098</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C84">
-        <v>128</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6629</v>
+        <v>6494</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6630</v>
+        <v>6496</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6936</v>
+        <v>6497</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>7004</v>
+        <v>6575</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>49</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>7005</v>
+        <v>6627</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7007</v>
+        <v>7004</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7885</v>
+        <v>7084</v>
       </c>
       <c r="B91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8649</v>
+        <v>7885</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C92">
-        <v>172</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8660</v>
+        <v>7886</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8673</v>
+        <v>7887</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C94">
-        <v>133</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8675</v>
+        <v>8216</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>137</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8753</v>
+        <v>8284</v>
       </c>
       <c r="B96">
         <v>2</v>
       </c>
       <c r="C96">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8754</v>
+        <v>8286</v>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97">
-        <v>173</v>
+        <v>322</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8926</v>
+        <v>8649</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>30</v>
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9085</v>
+        <v>8675</v>
       </c>
       <c r="B99">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>87</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9087</v>
+        <v>8754</v>
       </c>
       <c r="B100">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>34</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9373</v>
+        <v>8915</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9459</v>
+        <v>8926</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>9530</v>
+        <v>8938</v>
       </c>
       <c r="B103">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>9760</v>
+        <v>8939</v>
       </c>
       <c r="B104">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>34</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>9777</v>
+        <v>8943</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>197</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>9778</v>
+        <v>8963</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10147</v>
+        <v>9070</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>10170</v>
+        <v>9085</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C108">
-        <v>27</v>
+        <v>94</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>10532</v>
+        <v>9087</v>
       </c>
       <c r="B109">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C109">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>10716</v>
+        <v>9459</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C110">
         <v>7</v>
@@ -1595,161 +1595,161 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11134</v>
+        <v>9507</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>103</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11234</v>
+        <v>9530</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C112">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11402</v>
+        <v>9531</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C113">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11427</v>
+        <v>9777</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>243</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11492</v>
+        <v>9784</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11619</v>
+        <v>10170</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11681</v>
+        <v>10716</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>254</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11683</v>
+        <v>10717</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11773</v>
+        <v>10993</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11814</v>
+        <v>11134</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11868</v>
+        <v>11427</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>182</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12048</v>
+        <v>11619</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12050</v>
+        <v>11737</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12222</v>
+        <v>11738</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12506</v>
+        <v>11773</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -1760,84 +1760,84 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12511</v>
+        <v>11887</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12574</v>
+        <v>12050</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12612</v>
+        <v>12222</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12764</v>
+        <v>12506</v>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>353</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12923</v>
+        <v>12511</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12924</v>
+        <v>12612</v>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
       <c r="C131">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12925</v>
+        <v>12764</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>31</v>
+        <v>373</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>12979</v>
+        <v>12923</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -1848,101 +1848,101 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13115</v>
+        <v>12979</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>337</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13293</v>
+        <v>13115</v>
       </c>
       <c r="B135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>140</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19685</v>
+        <v>13244</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>19687</v>
+        <v>13293</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C137">
-        <v>59</v>
+        <v>200</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>19969</v>
+        <v>13928</v>
       </c>
       <c r="B138">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19981</v>
+        <v>18964</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19985</v>
+        <v>19685</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>20650</v>
+        <v>19981</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20927</v>
+        <v>20650</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>37</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="C143">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -1980,68 +1980,57 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23645</v>
+        <v>23235</v>
       </c>
       <c r="B146">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23992</v>
+        <v>23645</v>
       </c>
       <c r="B147">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C147">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24566</v>
+        <v>23992</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C148">
-        <v>151</v>
+        <v>27</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24670</v>
+        <v>24566</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>15</v>
+        <v>166</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24705</v>
+        <v>24669</v>
       </c>
       <c r="B150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C150">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>25960</v>
-      </c>
-      <c r="B151">
-        <v>2</v>
-      </c>
-      <c r="C151">
-        <v>127</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -418,230 +418,230 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>860</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>142</v>
+        <v>221</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>145</v>
+        <v>308</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>151</v>
+        <v>345</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>67</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>217</v>
+        <v>378</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>221</v>
+        <v>385</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>248</v>
+        <v>435</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>307</v>
+        <v>565</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>99</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>308</v>
+        <v>615</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>345</v>
+        <v>791</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>219</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>361</v>
+        <v>823</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>78</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>378</v>
+        <v>947</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>123</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>413</v>
+        <v>951</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>414</v>
+        <v>952</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>435</v>
+        <v>976</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>565</v>
+        <v>1049</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>589</v>
+        <v>1050</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>176</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>590</v>
+        <v>1055</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>790</v>
+        <v>1060</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -649,139 +649,139 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>791</v>
+        <v>1134</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>823</v>
+        <v>1163</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>944</v>
+        <v>1309</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>947</v>
+        <v>1406</v>
       </c>
       <c r="B28">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>950</v>
+        <v>1407</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C29">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>951</v>
+        <v>1409</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C30">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>952</v>
+        <v>1414</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C31">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>964</v>
+        <v>1450</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>976</v>
+        <v>1458</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1049</v>
+        <v>1490</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1050</v>
+        <v>1492</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1055</v>
+        <v>1504</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1060</v>
+        <v>1560</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -792,337 +792,337 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1243</v>
+        <v>1576</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1409</v>
+        <v>1728</v>
       </c>
       <c r="B39">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1414</v>
+        <v>1801</v>
       </c>
       <c r="B40">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1429</v>
+        <v>2054</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>65</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1446</v>
+        <v>2203</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1490</v>
+        <v>2422</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C43">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1492</v>
+        <v>2436</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>1668</v>
+        <v>2726</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>1801</v>
+        <v>2776</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>50</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2050</v>
+        <v>2778</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>307</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2054</v>
+        <v>2878</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>242</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2188</v>
+        <v>3016</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C49">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2203</v>
+        <v>3021</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2331</v>
+        <v>3258</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C51">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2422</v>
+        <v>3430</v>
       </c>
       <c r="B52">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C52">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2423</v>
+        <v>3434</v>
       </c>
       <c r="B53">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2424</v>
+        <v>3477</v>
       </c>
       <c r="B54">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2438</v>
+        <v>3674</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>27</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2774</v>
+        <v>3894</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2879</v>
+        <v>3898</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2916</v>
+        <v>3899</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3016</v>
+        <v>3905</v>
       </c>
       <c r="B59">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3258</v>
+        <v>4728</v>
       </c>
       <c r="B60">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>104</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3430</v>
+        <v>5020</v>
       </c>
       <c r="B61">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C61">
-        <v>36</v>
+        <v>261</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3434</v>
+        <v>5111</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3477</v>
+        <v>5152</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3576</v>
+        <v>5490</v>
       </c>
       <c r="B64">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3674</v>
+        <v>5491</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>121</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>3894</v>
+        <v>5493</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>77</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3898</v>
+        <v>5540</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>3899</v>
+        <v>5577</v>
       </c>
       <c r="B68">
         <v>3</v>
@@ -1133,414 +1133,414 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>3905</v>
+        <v>5585</v>
       </c>
       <c r="B69">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>4019</v>
+        <v>5652</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4232</v>
+        <v>5656</v>
       </c>
       <c r="B71">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5020</v>
+        <v>6097</v>
       </c>
       <c r="B72">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C72">
-        <v>261</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5111</v>
+        <v>6575</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>23</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5152</v>
+        <v>7004</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5490</v>
+        <v>7558</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5491</v>
+        <v>7886</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C76">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5493</v>
+        <v>8157</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C77">
-        <v>66</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5540</v>
+        <v>8216</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>87</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5577</v>
+        <v>8284</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5585</v>
+        <v>8286</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>255</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5652</v>
+        <v>8649</v>
       </c>
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81">
-        <v>28</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5656</v>
+        <v>8660</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>5733</v>
+        <v>8923</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C83">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>6098</v>
+        <v>8926</v>
       </c>
       <c r="B84">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6494</v>
+        <v>8938</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6496</v>
+        <v>8939</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6497</v>
+        <v>8943</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>19</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>6575</v>
+        <v>8963</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>141</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>6627</v>
+        <v>9070</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7004</v>
+        <v>9087</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C90">
-        <v>40</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7084</v>
+        <v>9357</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>65</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>7885</v>
+        <v>9374</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C92">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>7886</v>
+        <v>9459</v>
       </c>
       <c r="B93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>7887</v>
+        <v>9530</v>
       </c>
       <c r="B94">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C94">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8216</v>
+        <v>9531</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C95">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8284</v>
+        <v>9777</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>244</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8286</v>
+        <v>10717</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>322</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8649</v>
+        <v>10720</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C98">
-        <v>123</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>8675</v>
+        <v>10721</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C99">
-        <v>145</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>8754</v>
+        <v>10906</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>178</v>
+        <v>551</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>8915</v>
+        <v>11134</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C101">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>8926</v>
+        <v>11427</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>8938</v>
+        <v>11619</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>8939</v>
+        <v>11812</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>8943</v>
+        <v>11813</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>197</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>8963</v>
+        <v>11814</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1551,65 +1551,65 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>9070</v>
+        <v>11836</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>17</v>
+        <v>124</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>9085</v>
+        <v>11837</v>
       </c>
       <c r="B108">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>94</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>9087</v>
+        <v>11859</v>
       </c>
       <c r="B109">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>9459</v>
+        <v>11868</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>149</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>9507</v>
+        <v>11887</v>
       </c>
       <c r="B111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>9530</v>
+        <v>11911</v>
       </c>
       <c r="B112">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -1617,106 +1617,106 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>9531</v>
+        <v>12043</v>
       </c>
       <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113">
         <v>25</v>
-      </c>
-      <c r="C113">
-        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>9777</v>
+        <v>12048</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>9784</v>
+        <v>12050</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>10170</v>
+        <v>12222</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>10716</v>
+        <v>12229</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>10717</v>
+        <v>12253</v>
       </c>
       <c r="B118">
         <v>3</v>
       </c>
       <c r="C118">
-        <v>61</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>10993</v>
+        <v>12294</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C119">
-        <v>27</v>
+        <v>76</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11134</v>
+        <v>12489</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11427</v>
+        <v>12506</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11619</v>
+        <v>12511</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -1727,54 +1727,54 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>11737</v>
+        <v>12609</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>11738</v>
+        <v>12612</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>11773</v>
+        <v>12764</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>11887</v>
+        <v>12923</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>98</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12050</v>
+        <v>12952</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -1782,18 +1782,18 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12222</v>
+        <v>13030</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12506</v>
+        <v>13115</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12511</v>
+        <v>13269</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12612</v>
+        <v>13271</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -1826,210 +1826,254 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12764</v>
+        <v>13402</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>373</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>12923</v>
+        <v>18964</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>12979</v>
+        <v>19924</v>
       </c>
       <c r="B134">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>337</v>
+        <v>33</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13115</v>
+        <v>19981</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13244</v>
+        <v>19989</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13293</v>
+        <v>20650</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>200</v>
+        <v>116</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13928</v>
+        <v>20984</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>18964</v>
+        <v>21091</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C139">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19685</v>
+        <v>21783</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>19981</v>
+        <v>21793</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>33</v>
+        <v>242</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>20650</v>
+        <v>21806</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>116</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21806</v>
+        <v>21809</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21809</v>
+        <v>22326</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22364</v>
+        <v>22361</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23235</v>
+        <v>22364</v>
       </c>
       <c r="B146">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23645</v>
+        <v>22631</v>
       </c>
       <c r="B147">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>376</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23992</v>
+        <v>22634</v>
       </c>
       <c r="B148">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24566</v>
+        <v>23540</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C149">
-        <v>166</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
+        <v>23645</v>
+      </c>
+      <c r="B150">
+        <v>68</v>
+      </c>
+      <c r="C150">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>23994</v>
+      </c>
+      <c r="B151">
+        <v>29</v>
+      </c>
+      <c r="C151">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>24566</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
         <v>24669</v>
       </c>
-      <c r="B150">
-        <v>1</v>
-      </c>
-      <c r="C150">
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>24725</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
+      </c>
+      <c r="C154">
         <v>7</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -407,197 +407,197 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>164</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>221</v>
+        <v>88</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>308</v>
+        <v>94</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>345</v>
+        <v>142</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>219</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>378</v>
+        <v>144</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>385</v>
+        <v>159</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>435</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>565</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>615</v>
+        <v>217</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>791</v>
+        <v>247</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>823</v>
+        <v>305</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>947</v>
+        <v>308</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>951</v>
+        <v>336</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>952</v>
+        <v>414</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>976</v>
+        <v>417</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -605,524 +605,524 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1049</v>
+        <v>435</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1050</v>
+        <v>515</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1055</v>
+        <v>523</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1060</v>
+        <v>565</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1134</v>
+        <v>615</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1163</v>
+        <v>738</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>176</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1309</v>
+        <v>790</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1406</v>
+        <v>791</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1407</v>
+        <v>947</v>
       </c>
       <c r="B29">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C29">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1409</v>
+        <v>951</v>
       </c>
       <c r="B30">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C30">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1414</v>
+        <v>952</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1450</v>
+        <v>1007</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>44</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1458</v>
+        <v>1049</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1490</v>
+        <v>1055</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1492</v>
+        <v>1124</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>19</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1504</v>
+        <v>1243</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1560</v>
+        <v>1429</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1576</v>
+        <v>1446</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1728</v>
+        <v>1490</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1801</v>
+        <v>1504</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>52</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2054</v>
+        <v>1654</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>230</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2203</v>
+        <v>1656</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2422</v>
+        <v>1668</v>
       </c>
       <c r="B43">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>19</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2436</v>
+        <v>1801</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2726</v>
+        <v>2050</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>62</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2776</v>
+        <v>2109</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>137</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2778</v>
+        <v>2188</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>133</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2878</v>
+        <v>2203</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3016</v>
+        <v>2328</v>
       </c>
       <c r="B49">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3021</v>
+        <v>2331</v>
       </c>
       <c r="B50">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3258</v>
+        <v>2422</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>104</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3430</v>
+        <v>2424</v>
       </c>
       <c r="B52">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C52">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3434</v>
+        <v>2438</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3477</v>
+        <v>2776</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>27</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3674</v>
+        <v>2778</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>123</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3894</v>
+        <v>2859</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C56">
-        <v>77</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3898</v>
+        <v>2916</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3899</v>
+        <v>2991</v>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3905</v>
+        <v>3016</v>
       </c>
       <c r="B59">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4728</v>
+        <v>3258</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5020</v>
+        <v>3429</v>
       </c>
       <c r="B61">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C61">
-        <v>261</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5111</v>
+        <v>3434</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5152</v>
+        <v>3671</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5490</v>
+        <v>3673</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>51</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5491</v>
+        <v>3674</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>50</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5493</v>
+        <v>3894</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5540</v>
+        <v>3898</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>88</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5577</v>
+        <v>3899</v>
       </c>
       <c r="B68">
         <v>3</v>
@@ -1133,392 +1133,392 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5585</v>
+        <v>3905</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5652</v>
+        <v>4019</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5656</v>
+        <v>4232</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>28</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6097</v>
+        <v>5020</v>
       </c>
       <c r="B72">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="C72">
-        <v>35</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6575</v>
+        <v>5111</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>135</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>7004</v>
+        <v>5152</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>7558</v>
+        <v>5490</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>34</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7886</v>
+        <v>5491</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8157</v>
+        <v>5493</v>
       </c>
       <c r="B77">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8216</v>
+        <v>5540</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>45</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8284</v>
+        <v>5577</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>255</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8286</v>
+        <v>5585</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>255</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8649</v>
+        <v>5646</v>
       </c>
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81">
-        <v>92</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8660</v>
+        <v>5652</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8923</v>
+        <v>5654</v>
       </c>
       <c r="B83">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8926</v>
+        <v>5736</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8938</v>
+        <v>6097</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C85">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8939</v>
+        <v>6098</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C86">
-        <v>81</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8943</v>
+        <v>6158</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>195</v>
+        <v>135</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8963</v>
+        <v>6497</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9070</v>
+        <v>6630</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9087</v>
+        <v>7004</v>
       </c>
       <c r="B90">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>108</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9357</v>
+        <v>7084</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9374</v>
+        <v>7885</v>
       </c>
       <c r="B92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9459</v>
+        <v>7886</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9530</v>
+        <v>7887</v>
       </c>
       <c r="B94">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9531</v>
+        <v>8650</v>
       </c>
       <c r="B95">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>123</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9777</v>
+        <v>8915</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10717</v>
+        <v>8926</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>61</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10720</v>
+        <v>8938</v>
       </c>
       <c r="B98">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>51</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10721</v>
+        <v>8939</v>
       </c>
       <c r="B99">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10906</v>
+        <v>9207</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>551</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11134</v>
+        <v>9208</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C101">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11427</v>
+        <v>9209</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C102">
-        <v>8</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11619</v>
+        <v>9239</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11812</v>
+        <v>9459</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1529,21 +1529,21 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11813</v>
+        <v>9507</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11814</v>
+        <v>9530</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -1551,21 +1551,21 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11836</v>
+        <v>9531</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C107">
-        <v>124</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11837</v>
+        <v>9777</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
         <v>7</v>
@@ -1573,65 +1573,65 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11859</v>
+        <v>9784</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11868</v>
+        <v>10149</v>
       </c>
       <c r="B110">
         <v>3</v>
       </c>
       <c r="C110">
-        <v>149</v>
+        <v>483</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11887</v>
+        <v>11134</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C111">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11911</v>
+        <v>11399</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12043</v>
+        <v>11402</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12048</v>
+        <v>11427</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
         <v>8</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12050</v>
+        <v>11619</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -1650,84 +1650,84 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12222</v>
+        <v>11681</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>271</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12229</v>
+        <v>11684</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>77</v>
+        <v>304</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12253</v>
+        <v>11738</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12294</v>
+        <v>11739</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12489</v>
+        <v>11773</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12506</v>
+        <v>11838</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12511</v>
+        <v>11887</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12609</v>
+        <v>12050</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -1738,43 +1738,43 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12612</v>
+        <v>12222</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12764</v>
+        <v>12506</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>378</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12923</v>
+        <v>12511</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12952</v>
+        <v>12574</v>
       </c>
       <c r="B127">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -1782,172 +1782,172 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13030</v>
+        <v>12612</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13115</v>
+        <v>12791</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13269</v>
+        <v>12923</v>
       </c>
       <c r="B130">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13271</v>
+        <v>12924</v>
       </c>
       <c r="B131">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13402</v>
+        <v>12925</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>18964</v>
+        <v>13115</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>19924</v>
+        <v>13244</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>19981</v>
+        <v>13257</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C135">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19989</v>
+        <v>13258</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C136">
-        <v>33</v>
+        <v>360</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20650</v>
+        <v>13259</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>116</v>
+        <v>300</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20984</v>
+        <v>13962</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>21</v>
+        <v>101</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21091</v>
+        <v>20650</v>
       </c>
       <c r="B139">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21783</v>
+        <v>21793</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>44</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21793</v>
+        <v>21806</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>242</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21806</v>
+        <v>21809</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21809</v>
+        <v>22364</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -1958,76 +1958,76 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22326</v>
+        <v>23235</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22361</v>
+        <v>23645</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C145">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22364</v>
+        <v>23992</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>22631</v>
+        <v>24566</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>376</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>22634</v>
+        <v>24669</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23540</v>
+        <v>24705</v>
       </c>
       <c r="B149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>7</v>
+        <v>121</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>23645</v>
+        <v>24756</v>
       </c>
       <c r="B150">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -2035,46 +2035,13 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>23994</v>
+        <v>25278</v>
       </c>
       <c r="B151">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C151">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>24566</v>
-      </c>
-      <c r="B152">
-        <v>1</v>
-      </c>
-      <c r="C152">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>24669</v>
-      </c>
-      <c r="B153">
-        <v>1</v>
-      </c>
-      <c r="C153">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154">
-        <v>24725</v>
-      </c>
-      <c r="B154">
-        <v>2</v>
-      </c>
-      <c r="C154">
-        <v>7</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,274 +396,274 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
         <v>10</v>
-      </c>
-      <c r="C7">
-        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>94</v>
+        <v>201</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>63</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>205</v>
+        <v>308</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>206</v>
+        <v>336</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>217</v>
+        <v>345</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>247</v>
+        <v>361</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>46</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>308</v>
+        <v>413</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>85</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>336</v>
+        <v>418</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>56</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>417</v>
+        <v>479</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>435</v>
+        <v>523</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>515</v>
+        <v>560</v>
       </c>
       <c r="B22">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>109</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>523</v>
+        <v>563</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>78</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C24">
-        <v>95</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>615</v>
+        <v>924</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>738</v>
+        <v>949</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -671,362 +671,362 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>790</v>
+        <v>951</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>791</v>
+        <v>952</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>947</v>
+        <v>990</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>951</v>
+        <v>1163</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>52</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>952</v>
+        <v>1309</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1007</v>
+        <v>1447</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>137</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1049</v>
+        <v>1576</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1055</v>
+        <v>2050</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1124</v>
+        <v>2055</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>94</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1243</v>
+        <v>2057</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>51</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1429</v>
+        <v>2190</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1446</v>
+        <v>2203</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1490</v>
+        <v>2264</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1504</v>
+        <v>2365</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1654</v>
+        <v>2423</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C41">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1656</v>
+        <v>2424</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C42">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1668</v>
+        <v>2506</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>53</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1801</v>
+        <v>2935</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2050</v>
+        <v>2991</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2109</v>
+        <v>2992</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>20</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2188</v>
+        <v>3072</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2203</v>
+        <v>3073</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2328</v>
+        <v>3430</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C49">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2331</v>
+        <v>3434</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2422</v>
+        <v>3477</v>
       </c>
       <c r="B51">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2424</v>
+        <v>3478</v>
       </c>
       <c r="B52">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2438</v>
+        <v>3582</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2776</v>
+        <v>3671</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>137</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2778</v>
+        <v>3894</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2859</v>
+        <v>3915</v>
       </c>
       <c r="B56">
         <v>15</v>
       </c>
       <c r="C56">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2916</v>
+        <v>3970</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2991</v>
+        <v>4223</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3016</v>
+        <v>4866</v>
       </c>
       <c r="B59">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C59">
         <v>7</v>
@@ -1034,98 +1034,98 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3258</v>
+        <v>5152</v>
       </c>
       <c r="B60">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>104</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3429</v>
+        <v>5391</v>
       </c>
       <c r="B61">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3434</v>
+        <v>5577</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>46</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3671</v>
+        <v>5585</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>46</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3673</v>
+        <v>5812</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>121</v>
+        <v>404</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3674</v>
+        <v>6098</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C65">
-        <v>123</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>3894</v>
+        <v>6158</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>80</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3898</v>
+        <v>6293</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>3899</v>
+        <v>6294</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C68">
         <v>7</v>
@@ -1133,601 +1133,601 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>3905</v>
+        <v>6864</v>
       </c>
       <c r="B69">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>4019</v>
+        <v>7004</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4232</v>
+        <v>7885</v>
       </c>
       <c r="B71">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C71">
-        <v>100</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5020</v>
+        <v>7886</v>
       </c>
       <c r="B72">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C72">
-        <v>249</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5111</v>
+        <v>7887</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>23</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5152</v>
+        <v>8274</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5490</v>
+        <v>8283</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>119</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5491</v>
+        <v>8285</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>48</v>
+        <v>254</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5493</v>
+        <v>8286</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>254</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5540</v>
+        <v>8676</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>88</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5577</v>
+        <v>8939</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5585</v>
+        <v>8944</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5646</v>
+        <v>9070</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5652</v>
+        <v>9087</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C82">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>5654</v>
+        <v>9357</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>5736</v>
+        <v>9380</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6097</v>
+        <v>9430</v>
       </c>
       <c r="B85">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6098</v>
+        <v>9459</v>
       </c>
       <c r="B86">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6158</v>
+        <v>9530</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C87">
-        <v>135</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>6497</v>
+        <v>9841</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C88">
-        <v>19</v>
+        <v>375</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>6630</v>
+        <v>10574</v>
       </c>
       <c r="B89">
         <v>3</v>
       </c>
       <c r="C89">
-        <v>50</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7004</v>
+        <v>10582</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7084</v>
+        <v>10595</v>
       </c>
       <c r="B91">
         <v>3</v>
       </c>
       <c r="C91">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>7885</v>
+        <v>10596</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>7886</v>
+        <v>10609</v>
       </c>
       <c r="B93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>7887</v>
+        <v>10825</v>
       </c>
       <c r="B94">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C94">
-        <v>71</v>
+        <v>344</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8650</v>
+        <v>10897</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>123</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8915</v>
+        <v>11132</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C96">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8926</v>
+        <v>11134</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8938</v>
+        <v>11396</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98">
-        <v>82</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>8939</v>
+        <v>11410</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C99">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9207</v>
+        <v>11427</v>
       </c>
       <c r="B100">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9208</v>
+        <v>11435</v>
       </c>
       <c r="B101">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>17</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9209</v>
+        <v>11450</v>
       </c>
       <c r="B102">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>200</v>
+        <v>258</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>9239</v>
+        <v>11618</v>
       </c>
       <c r="B103">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>15</v>
+        <v>86</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>9459</v>
+        <v>11619</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>9507</v>
+        <v>11687</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>103</v>
+        <v>160</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>9530</v>
+        <v>11689</v>
       </c>
       <c r="B106">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>160</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>9531</v>
+        <v>11737</v>
       </c>
       <c r="B107">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>9777</v>
+        <v>11738</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>9784</v>
+        <v>11838</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>37</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>10149</v>
+        <v>11868</v>
       </c>
       <c r="B110">
         <v>3</v>
       </c>
       <c r="C110">
-        <v>483</v>
+        <v>148</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11134</v>
+        <v>11886</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11399</v>
+        <v>11911</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11402</v>
+        <v>12050</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11427</v>
+        <v>12139</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>67</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11619</v>
+        <v>12147</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11681</v>
+        <v>12222</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>271</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11684</v>
+        <v>12243</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>304</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11738</v>
+        <v>12252</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11739</v>
+        <v>12253</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C119">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11773</v>
+        <v>12269</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11838</v>
+        <v>12270</v>
       </c>
       <c r="B121">
         <v>2</v>
       </c>
       <c r="C121">
-        <v>254</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11887</v>
+        <v>12271</v>
       </c>
       <c r="B122">
         <v>2</v>
       </c>
       <c r="C122">
-        <v>98</v>
+        <v>35</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12050</v>
+        <v>12506</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -1738,109 +1738,109 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12222</v>
+        <v>12613</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12506</v>
+        <v>12638</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12511</v>
+        <v>12979</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>334</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12574</v>
+        <v>13033</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>610</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12612</v>
+        <v>13034</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>610</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12791</v>
+        <v>13117</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12923</v>
+        <v>13254</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C130">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12924</v>
+        <v>13402</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12925</v>
+        <v>13403</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13115</v>
+        <v>13406</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -1848,57 +1848,57 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13244</v>
+        <v>13407</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13257</v>
+        <v>13968</v>
       </c>
       <c r="B135">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13258</v>
+        <v>19879</v>
       </c>
       <c r="B136">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>360</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13259</v>
+        <v>19981</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C137">
-        <v>300</v>
+        <v>33</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13962</v>
+        <v>20649</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>101</v>
+        <v>59</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -1909,18 +1909,18 @@
         <v>1</v>
       </c>
       <c r="C139">
-        <v>63</v>
+        <v>78</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21793</v>
+        <v>21091</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C140">
-        <v>403</v>
+        <v>65</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -1947,32 +1947,32 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22364</v>
+        <v>22407</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23235</v>
+        <v>22408</v>
       </c>
       <c r="B144">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23645</v>
+        <v>23341</v>
       </c>
       <c r="B145">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -1980,29 +1980,29 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23992</v>
+        <v>23600</v>
       </c>
       <c r="B146">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C146">
-        <v>27</v>
+        <v>123</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>24566</v>
+        <v>23661</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>173</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24669</v>
+        <v>24254</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2013,35 +2013,57 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24705</v>
+        <v>24567</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C149">
-        <v>121</v>
+        <v>159</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24756</v>
+        <v>25278</v>
       </c>
       <c r="B150">
         <v>2</v>
       </c>
       <c r="C150">
-        <v>7</v>
+        <v>141</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>25278</v>
+        <v>25698</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C151">
-        <v>143</v>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>25699</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>25960</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,502 +396,502 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>54</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>283</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>78</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>78</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>321</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>54</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>217</v>
+        <v>159</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>308</v>
+        <v>217</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>336</v>
+        <v>248</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>321</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>361</v>
+        <v>308</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>202</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>413</v>
+        <v>345</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>42</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>418</v>
+        <v>560</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>138</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>468</v>
+        <v>947</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C19">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>479</v>
+        <v>949</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>523</v>
+        <v>990</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>77</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>560</v>
+        <v>1050</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>563</v>
+        <v>1309</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>590</v>
+        <v>1409</v>
       </c>
       <c r="B24">
         <v>15</v>
       </c>
       <c r="C24">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>924</v>
+        <v>1413</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>949</v>
+        <v>1414</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>951</v>
+        <v>1447</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>952</v>
+        <v>1504</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>40</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>990</v>
+        <v>1576</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1163</v>
+        <v>2050</v>
       </c>
       <c r="B30">
         <v>3</v>
       </c>
       <c r="C30">
-        <v>176</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1309</v>
+        <v>2055</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>28</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1447</v>
+        <v>2190</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1576</v>
+        <v>2203</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2050</v>
+        <v>2264</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>236</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2055</v>
+        <v>2324</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>238</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2057</v>
+        <v>2365</v>
       </c>
       <c r="B36">
         <v>3</v>
       </c>
       <c r="C36">
-        <v>238</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2190</v>
+        <v>2422</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2203</v>
+        <v>2423</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2264</v>
+        <v>2424</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2365</v>
+        <v>2497</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2423</v>
+        <v>2504</v>
       </c>
       <c r="B41">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>19</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2424</v>
+        <v>2859</v>
       </c>
       <c r="B42">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C42">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2506</v>
+        <v>2991</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>114</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2935</v>
+        <v>2992</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2991</v>
+        <v>3016</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C45">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2992</v>
+        <v>3072</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="B47">
         <v>3</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3073</v>
+        <v>3434</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48">
         <v>7</v>
@@ -913,87 +913,87 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3430</v>
+        <v>3478</v>
       </c>
       <c r="B49">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3434</v>
+        <v>3582</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3477</v>
+        <v>3671</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3478</v>
+        <v>3894</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3582</v>
+        <v>3905</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3671</v>
+        <v>3915</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C54">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3894</v>
+        <v>3970</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3915</v>
+        <v>4223</v>
       </c>
       <c r="B56">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C56">
         <v>7</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3970</v>
+        <v>4866</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4223</v>
+        <v>5152</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4866</v>
+        <v>5391</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -1034,95 +1034,95 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5152</v>
+        <v>5490</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5391</v>
+        <v>5577</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5577</v>
+        <v>5585</v>
       </c>
       <c r="B62">
         <v>3</v>
       </c>
       <c r="C62">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5585</v>
+        <v>5646</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5812</v>
+        <v>5656</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>404</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>6098</v>
+        <v>6097</v>
       </c>
       <c r="B65">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C65">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>6158</v>
+        <v>6098</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C66">
-        <v>265</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6293</v>
+        <v>6158</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6294</v>
+        <v>6293</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -1144,197 +1144,197 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>7004</v>
+        <v>6936</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>40</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>7885</v>
+        <v>6952</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>71</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>7886</v>
+        <v>7004</v>
       </c>
       <c r="B72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7887</v>
+        <v>7704</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>71</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8274</v>
+        <v>7708</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>233</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>8283</v>
+        <v>7885</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C75">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>8285</v>
+        <v>7886</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C76">
-        <v>254</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8286</v>
+        <v>8283</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8676</v>
+        <v>8285</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>189</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8939</v>
+        <v>8286</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>78</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8944</v>
+        <v>8360</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>112</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>9070</v>
+        <v>8649</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>17</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>9087</v>
+        <v>8651</v>
       </c>
       <c r="B82">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>54</v>
+        <v>367</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>9357</v>
+        <v>8676</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>25</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>9380</v>
+        <v>8944</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>8</v>
+        <v>112</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9430</v>
+        <v>9208</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9459</v>
+        <v>9380</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9530</v>
+        <v>9459</v>
       </c>
       <c r="B87">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C87">
         <v>7</v>
@@ -1342,65 +1342,65 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9841</v>
+        <v>9507</v>
       </c>
       <c r="B88">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>375</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>10574</v>
+        <v>9530</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C89">
-        <v>270</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>10582</v>
+        <v>9840</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>417</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10595</v>
+        <v>10574</v>
       </c>
       <c r="B91">
         <v>3</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>274</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10596</v>
+        <v>10582</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10609</v>
+        <v>10595</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,24 +1408,24 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10825</v>
+        <v>10596</v>
       </c>
       <c r="B94">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>344</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10897</v>
+        <v>10993</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1452,175 +1452,175 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11396</v>
+        <v>11427</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98">
-        <v>9</v>
+        <v>252</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11410</v>
+        <v>11435</v>
       </c>
       <c r="B99">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11427</v>
+        <v>11450</v>
       </c>
       <c r="B100">
         <v>2</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>248</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11435</v>
+        <v>11618</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>259</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11450</v>
+        <v>11619</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>258</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11618</v>
+        <v>11689</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>86</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11619</v>
+        <v>11738</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>81</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11687</v>
+        <v>11848</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>160</v>
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11689</v>
+        <v>11868</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C106">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11737</v>
+        <v>11886</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>30</v>
+        <v>97</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11738</v>
+        <v>11887</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>30</v>
+        <v>195</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11838</v>
+        <v>11911</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>125</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11868</v>
+        <v>12050</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>148</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11886</v>
+        <v>12139</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>98</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11911</v>
+        <v>12222</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12050</v>
+        <v>12243</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -1628,43 +1628,43 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12139</v>
+        <v>12252</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12147</v>
+        <v>12253</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12222</v>
+        <v>12269</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12243</v>
+        <v>12270</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -1672,90 +1672,90 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12252</v>
+        <v>12271</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12253</v>
+        <v>12350</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12269</v>
+        <v>12506</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12270</v>
+        <v>12613</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12271</v>
+        <v>12638</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12506</v>
+        <v>12721</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12613</v>
+        <v>12722</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>141</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12638</v>
+        <v>12776</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -1763,10 +1763,10 @@
         <v>12979</v>
       </c>
       <c r="B126">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>334</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="C127">
-        <v>610</v>
+        <v>599</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -1788,7 +1788,7 @@
         <v>3</v>
       </c>
       <c r="C128">
-        <v>610</v>
+        <v>602</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -1804,13 +1804,13 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13254</v>
+        <v>13258</v>
       </c>
       <c r="B130">
         <v>29</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -1859,13 +1859,13 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13968</v>
+        <v>13928</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -1881,73 +1881,73 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>19981</v>
+        <v>19969</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20649</v>
+        <v>19981</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>20650</v>
+        <v>20649</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21091</v>
+        <v>20650</v>
       </c>
       <c r="B140">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21806</v>
+        <v>21091</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C141">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21809</v>
+        <v>21269</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>309</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22407</v>
+        <v>21806</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22408</v>
+        <v>21809</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -1969,43 +1969,43 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23341</v>
+        <v>22407</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23600</v>
+        <v>22408</v>
       </c>
       <c r="B146">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23661</v>
+        <v>23247</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C147">
-        <v>173</v>
+        <v>51</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24254</v>
+        <v>23341</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -2013,43 +2013,43 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24567</v>
+        <v>23528</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>159</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>25278</v>
+        <v>23661</v>
       </c>
       <c r="B150">
         <v>2</v>
       </c>
       <c r="C150">
-        <v>141</v>
+        <v>104</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>25698</v>
+        <v>23961</v>
       </c>
       <c r="B151">
         <v>3</v>
       </c>
       <c r="C151">
-        <v>390</v>
+        <v>209</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>25699</v>
+        <v>24254</v>
       </c>
       <c r="B152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C152">
         <v>7</v>
@@ -2057,13 +2057,46 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>25960</v>
+        <v>25586</v>
       </c>
       <c r="B153">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>135</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>25588</v>
+      </c>
+      <c r="B154">
+        <v>3</v>
+      </c>
+      <c r="C154">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>25698</v>
+      </c>
+      <c r="B155">
+        <v>3</v>
+      </c>
+      <c r="C155">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>25699</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,13 +396,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>113</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -424,532 +424,532 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>286</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>78</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>144</v>
+        <v>308</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>151</v>
+        <v>336</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>159</v>
+        <v>345</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>217</v>
+        <v>346</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>585</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>248</v>
+        <v>361</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>27</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>308</v>
+        <v>378</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>336</v>
+        <v>417</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>320</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>560</v>
+        <v>515</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C18">
-        <v>48</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>947</v>
+        <v>523</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>949</v>
+        <v>560</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>990</v>
+        <v>624</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>27</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1050</v>
+        <v>944</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1309</v>
+        <v>947</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C23">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1409</v>
+        <v>949</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1413</v>
+        <v>950</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1414</v>
+        <v>1005</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1447</v>
+        <v>1007</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>19</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1504</v>
+        <v>1124</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>165</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1576</v>
+        <v>1163</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29">
-        <v>24</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2050</v>
+        <v>1309</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>238</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2055</v>
+        <v>1409</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C31">
-        <v>240</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2190</v>
+        <v>1413</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2203</v>
+        <v>1414</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2264</v>
+        <v>1429</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2324</v>
+        <v>1446</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2365</v>
+        <v>1450</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2422</v>
+        <v>1576</v>
       </c>
       <c r="B37">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2423</v>
+        <v>1656</v>
       </c>
       <c r="B38">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2424</v>
+        <v>2013</v>
       </c>
       <c r="B39">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2497</v>
+        <v>2049</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>160</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2504</v>
+        <v>2054</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>284</v>
+        <v>313</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2859</v>
+        <v>2055</v>
       </c>
       <c r="B42">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>36</v>
+        <v>235</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2991</v>
+        <v>2057</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2992</v>
+        <v>2109</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>79</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3016</v>
+        <v>2203</v>
       </c>
       <c r="B45">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3072</v>
+        <v>2324</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3073</v>
+        <v>2423</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3434</v>
+        <v>2424</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3478</v>
+        <v>2778</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49">
-        <v>38</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3582</v>
+        <v>2859</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3671</v>
+        <v>2912</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3894</v>
+        <v>2992</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52">
         <v>7</v>
@@ -957,43 +957,43 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3905</v>
+        <v>3073</v>
       </c>
       <c r="B53">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3915</v>
+        <v>3429</v>
       </c>
       <c r="B54">
         <v>15</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3970</v>
+        <v>3430</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>4223</v>
+        <v>3434</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C56">
         <v>7</v>
@@ -1001,21 +1001,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4866</v>
+        <v>3477</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5152</v>
+        <v>3582</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -1023,109 +1023,109 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5391</v>
+        <v>3671</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5490</v>
+        <v>3894</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5577</v>
+        <v>3905</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C61">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5585</v>
+        <v>3915</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C62">
-        <v>135</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5646</v>
+        <v>4223</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5656</v>
+        <v>4866</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>6097</v>
+        <v>5020</v>
       </c>
       <c r="B65">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="C65">
-        <v>46</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>6098</v>
+        <v>5152</v>
       </c>
       <c r="B66">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6158</v>
+        <v>5165</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>265</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6293</v>
+        <v>5577</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>7</v>
@@ -1133,10 +1133,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6864</v>
+        <v>5585</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>7</v>
@@ -1144,271 +1144,271 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6936</v>
+        <v>5646</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>317</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6952</v>
+        <v>5656</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>94</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>7004</v>
+        <v>5812</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>40</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7704</v>
+        <v>5813</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>172</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>7708</v>
+        <v>6097</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C74">
-        <v>169</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>7885</v>
+        <v>6098</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C75">
-        <v>71</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7886</v>
+        <v>6952</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>72</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8283</v>
+        <v>7007</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>253</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8285</v>
+        <v>7084</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>253</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8286</v>
+        <v>7885</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C79">
-        <v>253</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8360</v>
+        <v>7886</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C80">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8649</v>
+        <v>8216</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>124</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8651</v>
+        <v>8286</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>367</v>
+        <v>242</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8676</v>
+        <v>8753</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8944</v>
+        <v>8938</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>112</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>9208</v>
+        <v>8943</v>
       </c>
       <c r="B85">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>18</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9380</v>
+        <v>9239</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C86">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9459</v>
+        <v>9380</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9507</v>
+        <v>9459</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>101</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9530</v>
+        <v>9491</v>
       </c>
       <c r="B89">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9840</v>
+        <v>9507</v>
       </c>
       <c r="B90">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>417</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10574</v>
+        <v>9530</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C91">
-        <v>274</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10582</v>
+        <v>9877</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10595</v>
+        <v>10574</v>
       </c>
       <c r="B93">
         <v>3</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10596</v>
+        <v>10595</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -1419,208 +1419,208 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10993</v>
+        <v>10596</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>11132</v>
+        <v>11085</v>
       </c>
       <c r="B96">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>8</v>
+        <v>276</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>11134</v>
+        <v>11092</v>
       </c>
       <c r="B97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11427</v>
+        <v>11132</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C98">
-        <v>252</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11435</v>
+        <v>11134</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C99">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11450</v>
+        <v>11427</v>
       </c>
       <c r="B100">
         <v>2</v>
       </c>
       <c r="C100">
-        <v>248</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11618</v>
+        <v>11435</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11619</v>
+        <v>11450</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>83</v>
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11689</v>
+        <v>11619</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>160</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11738</v>
+        <v>11681</v>
       </c>
       <c r="B104">
         <v>2</v>
       </c>
       <c r="C104">
-        <v>29</v>
+        <v>135</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11848</v>
+        <v>11683</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>74</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11868</v>
+        <v>11690</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11886</v>
+        <v>11738</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>97</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11887</v>
+        <v>11793</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>195</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11911</v>
+        <v>11835</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>12050</v>
+        <v>11836</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>251</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>12139</v>
+        <v>11886</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>67</v>
+        <v>96</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>12222</v>
+        <v>11887</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>21</v>
+        <v>127</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12243</v>
+        <v>11911</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12252</v>
+        <v>12050</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -1639,32 +1639,32 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12253</v>
+        <v>12222</v>
       </c>
       <c r="B115">
         <v>3</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12269</v>
+        <v>12243</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12270</v>
+        <v>12253</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12271</v>
+        <v>12269</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -1683,21 +1683,21 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12350</v>
+        <v>12270</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>1192</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12506</v>
+        <v>12271</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,117 +1705,117 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12613</v>
+        <v>12350</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>394</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12638</v>
+        <v>12506</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12721</v>
+        <v>12720</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>282</v>
+        <v>140</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12722</v>
+        <v>12764</v>
       </c>
       <c r="B124">
         <v>2</v>
       </c>
       <c r="C124">
-        <v>141</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12776</v>
+        <v>12979</v>
       </c>
       <c r="B125">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12979</v>
+        <v>13023</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C126">
-        <v>21</v>
+        <v>293</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13033</v>
+        <v>13028</v>
       </c>
       <c r="B127">
         <v>3</v>
       </c>
       <c r="C127">
-        <v>599</v>
+        <v>148</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13034</v>
+        <v>13117</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>602</v>
+        <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13117</v>
+        <v>13258</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C129">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13258</v>
+        <v>13402</v>
       </c>
       <c r="B130">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13402</v>
+        <v>13403</v>
       </c>
       <c r="B131">
         <v>3</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13403</v>
+        <v>13406</v>
       </c>
       <c r="B132">
         <v>3</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13406</v>
+        <v>13407</v>
       </c>
       <c r="B133">
         <v>3</v>
@@ -1848,13 +1848,13 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13407</v>
+        <v>13488</v>
       </c>
       <c r="B134">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -1865,18 +1865,18 @@
         <v>1</v>
       </c>
       <c r="C135">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19879</v>
+        <v>18964</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -1887,7 +1887,7 @@
         <v>29</v>
       </c>
       <c r="C137">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -1903,62 +1903,62 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>20649</v>
+        <v>20650</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>20650</v>
+        <v>21809</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21091</v>
+        <v>22407</v>
       </c>
       <c r="B141">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21269</v>
+        <v>22408</v>
       </c>
       <c r="B142">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>309</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21806</v>
+        <v>23247</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C143">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21809</v>
+        <v>23528</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -1969,134 +1969,68 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22407</v>
+        <v>23661</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>8</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22408</v>
+        <v>25278</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>279</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23247</v>
+        <v>25586</v>
       </c>
       <c r="B147">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23341</v>
+        <v>25588</v>
       </c>
       <c r="B148">
         <v>3</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23528</v>
+        <v>25698</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C149">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>23661</v>
+        <v>25960</v>
       </c>
       <c r="B150">
         <v>2</v>
       </c>
       <c r="C150">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>23961</v>
-      </c>
-      <c r="B151">
-        <v>3</v>
-      </c>
-      <c r="C151">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>24254</v>
-      </c>
-      <c r="B152">
-        <v>1</v>
-      </c>
-      <c r="C152">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>25586</v>
-      </c>
-      <c r="B153">
-        <v>3</v>
-      </c>
-      <c r="C153">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154">
-        <v>25588</v>
-      </c>
-      <c r="B154">
-        <v>3</v>
-      </c>
-      <c r="C154">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155">
-        <v>25698</v>
-      </c>
-      <c r="B155">
-        <v>3</v>
-      </c>
-      <c r="C155">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156">
-        <v>25699</v>
-      </c>
-      <c r="B156">
-        <v>2</v>
-      </c>
-      <c r="C156">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1123.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,35 +396,35 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -440,24 +440,24 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -468,40 +468,40 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>56</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>213</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -512,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>585</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -523,433 +523,433 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>362</v>
+        <v>416</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>378</v>
+        <v>523</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>417</v>
+        <v>560</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>434</v>
+        <v>589</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>515</v>
+        <v>593</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>236</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>523</v>
+        <v>823</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>77</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>560</v>
+        <v>949</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>624</v>
+        <v>952</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>178</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>944</v>
+        <v>990</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>22</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>947</v>
+        <v>1005</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>949</v>
+        <v>1007</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>950</v>
+        <v>1049</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1005</v>
+        <v>1124</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1007</v>
+        <v>1309</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>134</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1124</v>
+        <v>1414</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C28">
-        <v>93</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1163</v>
+        <v>1429</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>176</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1309</v>
+        <v>1446</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>28</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1409</v>
+        <v>1523</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1413</v>
+        <v>1576</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1414</v>
+        <v>1668</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1429</v>
+        <v>2049</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>87</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1446</v>
+        <v>2055</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>132</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1450</v>
+        <v>2057</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>41</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1576</v>
+        <v>2203</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1656</v>
+        <v>2324</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2013</v>
+        <v>2423</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2049</v>
+        <v>2424</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C40">
-        <v>277</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2054</v>
+        <v>2504</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>313</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2055</v>
+        <v>2778</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>235</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2057</v>
+        <v>2859</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C43">
-        <v>238</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2109</v>
+        <v>2985</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>20</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2203</v>
+        <v>3073</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2324</v>
+        <v>3429</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2423</v>
+        <v>3477</v>
       </c>
       <c r="B47">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2424</v>
+        <v>3582</v>
       </c>
       <c r="B48">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2778</v>
+        <v>3673</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49">
-        <v>137</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2859</v>
+        <v>3894</v>
       </c>
       <c r="B50">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2912</v>
+        <v>3905</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C51">
-        <v>24</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2992</v>
+        <v>3915</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C52">
         <v>7</v>
@@ -957,10 +957,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3073</v>
+        <v>4223</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -968,51 +968,51 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3429</v>
+        <v>4866</v>
       </c>
       <c r="B54">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3430</v>
+        <v>5452</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3434</v>
+        <v>5494</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3477</v>
+        <v>5577</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3582</v>
+        <v>5585</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -1023,87 +1023,87 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3671</v>
+        <v>5646</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3894</v>
+        <v>5656</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3905</v>
+        <v>5812</v>
       </c>
       <c r="B61">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>80</v>
+        <v>586</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3915</v>
+        <v>5813</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>300</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4223</v>
+        <v>6098</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4866</v>
+        <v>6356</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5020</v>
+        <v>6360</v>
       </c>
       <c r="B65">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>249</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5152</v>
+        <v>6496</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -1111,362 +1111,362 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5165</v>
+        <v>6935</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>24</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5577</v>
+        <v>6936</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5585</v>
+        <v>7004</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5646</v>
+        <v>7007</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5656</v>
+        <v>7704</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>28</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5812</v>
+        <v>7885</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C72">
-        <v>1152</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5813</v>
+        <v>7886</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>300</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6097</v>
+        <v>8274</v>
       </c>
       <c r="B74">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>45</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6098</v>
+        <v>8651</v>
       </c>
       <c r="B75">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>38</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6952</v>
+        <v>8939</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>188</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7007</v>
+        <v>8943</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>380</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7084</v>
+        <v>9081</v>
       </c>
       <c r="B78">
         <v>3</v>
       </c>
       <c r="C78">
-        <v>63</v>
+        <v>314</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7885</v>
+        <v>9380</v>
       </c>
       <c r="B79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>71</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7886</v>
+        <v>9459</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8216</v>
+        <v>9491</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C81">
-        <v>45</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8286</v>
+        <v>9507</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>242</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8753</v>
+        <v>9784</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>180</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8938</v>
+        <v>9877</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C84">
-        <v>78</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8943</v>
+        <v>10446</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C85">
-        <v>203</v>
+        <v>879</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>9239</v>
+        <v>10449</v>
       </c>
       <c r="B86">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C86">
-        <v>9</v>
+        <v>866</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9380</v>
+        <v>10450</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C87">
-        <v>8</v>
+        <v>866</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9459</v>
+        <v>10468</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>866</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9491</v>
+        <v>10595</v>
       </c>
       <c r="B89">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>1199</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9507</v>
+        <v>10596</v>
       </c>
       <c r="B90">
         <v>3</v>
       </c>
       <c r="C90">
-        <v>104</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9530</v>
+        <v>10720</v>
       </c>
       <c r="B91">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9877</v>
+        <v>11085</v>
       </c>
       <c r="B92">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>21</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10574</v>
+        <v>11088</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>10595</v>
+        <v>11089</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>10596</v>
+        <v>11092</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>11085</v>
+        <v>11132</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C96">
-        <v>276</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>11092</v>
+        <v>11134</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C97">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11132</v>
+        <v>11234</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11134</v>
+        <v>11427</v>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C99">
         <v>8</v>
@@ -1474,90 +1474,90 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11427</v>
+        <v>11435</v>
       </c>
       <c r="B100">
         <v>2</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>252</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11435</v>
+        <v>11450</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11450</v>
+        <v>11619</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>254</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11619</v>
+        <v>11683</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11681</v>
+        <v>11690</v>
       </c>
       <c r="B104">
         <v>2</v>
       </c>
       <c r="C104">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11683</v>
+        <v>11737</v>
       </c>
       <c r="B105">
         <v>2</v>
       </c>
       <c r="C105">
-        <v>173</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11690</v>
+        <v>11739</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106">
-        <v>154</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11738</v>
+        <v>11772</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>29</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1573,57 +1573,57 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11835</v>
+        <v>11836</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>125</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11836</v>
+        <v>11886</v>
       </c>
       <c r="B110">
         <v>2</v>
       </c>
       <c r="C110">
-        <v>251</v>
+        <v>191</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11886</v>
+        <v>11911</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11887</v>
+        <v>11914</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>127</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11911</v>
+        <v>12043</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -1661,7 +1661,7 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12253</v>
+        <v>12252</v>
       </c>
       <c r="B117">
         <v>3</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12269</v>
+        <v>12253</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12270</v>
+        <v>12269</v>
       </c>
       <c r="B119">
         <v>2</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12271</v>
+        <v>12270</v>
       </c>
       <c r="B120">
         <v>2</v>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12350</v>
+        <v>12271</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>394</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -1733,18 +1733,18 @@
         <v>2</v>
       </c>
       <c r="C123">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12764</v>
+        <v>12721</v>
       </c>
       <c r="B124">
         <v>2</v>
       </c>
       <c r="C124">
-        <v>377</v>
+        <v>283</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -1766,7 +1766,7 @@
         <v>3</v>
       </c>
       <c r="C126">
-        <v>293</v>
+        <v>595</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="C127">
-        <v>148</v>
+        <v>74</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -1793,18 +1793,18 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13258</v>
+        <v>13402</v>
       </c>
       <c r="B129">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13402</v>
+        <v>13403</v>
       </c>
       <c r="B130">
         <v>3</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13403</v>
+        <v>13406</v>
       </c>
       <c r="B131">
         <v>3</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13406</v>
+        <v>13407</v>
       </c>
       <c r="B132">
         <v>3</v>
@@ -1837,68 +1837,68 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13407</v>
+        <v>13485</v>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13488</v>
+        <v>13486</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>60</v>
+        <v>124</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13928</v>
+        <v>13487</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>18964</v>
+        <v>13928</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>19969</v>
+        <v>18964</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>19981</v>
+        <v>19969</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C138">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -1914,18 +1914,18 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21809</v>
+        <v>20927</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22407</v>
+        <v>20984</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -1936,100 +1936,155 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22408</v>
+        <v>21088</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>107</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23247</v>
+        <v>21806</v>
       </c>
       <c r="B143">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23528</v>
+        <v>21809</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23661</v>
+        <v>22316</v>
       </c>
       <c r="B145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>25278</v>
+        <v>22407</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>279</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>25586</v>
+        <v>22408</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>25588</v>
+        <v>23247</v>
       </c>
       <c r="B148">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C148">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>25698</v>
+        <v>23341</v>
       </c>
       <c r="B149">
         <v>3</v>
       </c>
       <c r="C149">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
+        <v>23528</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>23661</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>25278</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>25586</v>
+      </c>
+      <c r="B153">
+        <v>3</v>
+      </c>
+      <c r="C153">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>25589</v>
+      </c>
+      <c r="B154">
+        <v>3</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
         <v>25960</v>
       </c>
-      <c r="B150">
-        <v>2</v>
-      </c>
-      <c r="C150">
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155">
         <v>135</v>
       </c>
     </row>
